--- a/Result/profitability/4111.xlsx
+++ b/Result/profitability/4111.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.11</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6224999999999999</v>
+        <v>0.67125</v>
       </c>
       <c r="N2" t="n">
-        <v>37.1325</v>
+        <v>37.54125000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.14</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5962499999999999</v>
+        <v>0.5862499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>35.9975</v>
+        <v>35.97375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.11</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5075000000000001</v>
+        <v>0.515</v>
       </c>
       <c r="N4" t="n">
-        <v>34.27375</v>
+        <v>34.24125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.26</v>
       </c>
       <c r="M5" t="n">
-        <v>0.455</v>
+        <v>0.47125</v>
       </c>
       <c r="N5" t="n">
-        <v>32.9425</v>
+        <v>32.55875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.28</v>
       </c>
       <c r="M6" t="n">
-        <v>0.41375</v>
+        <v>0.4125</v>
       </c>
       <c r="N6" t="n">
-        <v>31.7125</v>
+        <v>31.6025</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>0.13</v>
       </c>
       <c r="M7" t="n">
-        <v>0.33625</v>
+        <v>0.33375</v>
       </c>
       <c r="N7" t="n">
-        <v>30.25125</v>
+        <v>29.96</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>0.24875</v>
+        <v>0.22875</v>
       </c>
       <c r="N8" t="n">
-        <v>28.43375</v>
+        <v>28.03625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>375</v>
+      </c>
+      <c r="D75" t="n">
+        <v>233</v>
+      </c>
+      <c r="E75" t="n">
+        <v>142</v>
+      </c>
+      <c r="F75" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="G75" t="n">
+        <v>52</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>13.84%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>60</v>
+      </c>
+      <c r="K75" t="n">
+        <v>44</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.7012499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1777777777777778</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.07757989753598438</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2131147540983607</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.07509784735812131</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
